--- a/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
+++ b/wanlong_service_retail_orders_fy_2025-05-01_2026-04-30.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度零售" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度零售明细" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="年度零售" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="支付明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="支付流水" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="年度零售明细" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -66,16 +72,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -753,7 +762,7 @@
           <t>正/闭</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="4" t="inlineStr">
         <is>
           <t>七色米订单号</t>
         </is>
@@ -7133,7 +7142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7144,6 +7153,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7187,6 +7197,11 @@
           <t>时间</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7222,6 +7237,11 @@
           <t>00:40:20</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>苍杰（测试）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7257,6 +7277,11 @@
           <t>10:35:58</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>苍杰（测试）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7297,6 +7322,11 @@
           <t>12:11:07</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7337,6 +7367,11 @@
           <t>12:18:12</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7377,6 +7412,11 @@
           <t>17:34:33</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7417,6 +7457,11 @@
           <t>10:37:08</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7457,6 +7502,11 @@
           <t>11:57:03</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7497,6 +7547,11 @@
           <t>13:49:22</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7537,6 +7592,11 @@
           <t>15:36:14</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7572,6 +7632,11 @@
           <t>14:29:00</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7612,6 +7677,11 @@
           <t>12:24:51</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7652,6 +7722,11 @@
           <t>15:48:40</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7692,6 +7767,11 @@
           <t>15:34:13</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7732,6 +7812,11 @@
           <t>11:19:44</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7767,6 +7852,11 @@
           <t>16:21:03</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7807,6 +7897,11 @@
           <t>09:34:29</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7847,6 +7942,11 @@
           <t>14:31:32</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7887,6 +7987,11 @@
           <t>14:10:50</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7922,6 +8027,11 @@
           <t>13:53:04</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7962,6 +8072,11 @@
           <t>13:16:42</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8002,6 +8117,11 @@
           <t>12:44:15</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8042,6 +8162,11 @@
           <t>11:38:48</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8082,6 +8207,11 @@
           <t>12:44:42</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>白雪景-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8122,6 +8252,11 @@
           <t>15:53:50</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8160,6 +8295,11 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>13:28:36</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>王政-工作号</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8724,7 @@
       <c r="G2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -8612,7 +8752,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="R2" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="S2" t="inlineStr">
@@ -8694,7 +8834,7 @@
           <t>WF_LS_251201_00001</t>
         </is>
       </c>
-      <c r="AM2" s="6" t="n">
+      <c r="AM2" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="AN2" t="inlineStr">
@@ -8795,7 +8935,7 @@
       <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -8823,7 +8963,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="R3" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="S3" t="inlineStr">
@@ -8905,7 +9045,7 @@
           <t>WF_LS_251201_00002</t>
         </is>
       </c>
-      <c r="AM3" s="6" t="n">
+      <c r="AM3" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="AN3" t="inlineStr">
@@ -9006,7 +9146,7 @@
       <c r="G4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="5" t="n">
         <v>45996</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -9034,7 +9174,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="R4" s="5" t="n">
         <v>45996</v>
       </c>
       <c r="S4" t="inlineStr">
@@ -9116,7 +9256,7 @@
           <t>WF_LS_251205_00001</t>
         </is>
       </c>
-      <c r="AM4" s="6" t="n">
+      <c r="AM4" s="5" t="n">
         <v>45996</v>
       </c>
       <c r="AN4" t="inlineStr">
@@ -9217,7 +9357,7 @@
       <c r="G5" t="n">
         <v>12</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -9245,7 +9385,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="R5" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="S5" t="inlineStr">
@@ -9327,7 +9467,7 @@
           <t>WF_LS_251206_00001</t>
         </is>
       </c>
-      <c r="AM5" s="6" t="n">
+      <c r="AM5" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="AN5" t="inlineStr">
@@ -9428,7 +9568,7 @@
       <c r="G6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -9456,7 +9596,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="S6" t="inlineStr">
@@ -9538,7 +9678,7 @@
           <t>WF_LS_251206_00002</t>
         </is>
       </c>
-      <c r="AM6" s="6" t="n">
+      <c r="AM6" s="5" t="n">
         <v>45997</v>
       </c>
       <c r="AN6" t="inlineStr">
@@ -9639,7 +9779,7 @@
       <c r="G7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="5" t="n">
         <v>46006</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -9667,7 +9807,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="R7" s="5" t="n">
         <v>46006</v>
       </c>
       <c r="S7" t="inlineStr">
@@ -9749,7 +9889,7 @@
           <t>WF_LS_251215_00001</t>
         </is>
       </c>
-      <c r="AM7" s="6" t="n">
+      <c r="AM7" s="5" t="n">
         <v>46006</v>
       </c>
       <c r="AN7" t="inlineStr">
@@ -9850,7 +9990,7 @@
       <c r="G8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="5" t="n">
         <v>46010</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -9878,7 +10018,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="R8" s="5" t="n">
         <v>46010</v>
       </c>
       <c r="S8" t="inlineStr">
@@ -9960,7 +10100,7 @@
           <t>WF_LS_251219_00001</t>
         </is>
       </c>
-      <c r="AM8" s="6" t="n">
+      <c r="AM8" s="5" t="n">
         <v>46010</v>
       </c>
       <c r="AN8" t="inlineStr">
@@ -10061,7 +10201,7 @@
       <c r="G9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H9" s="5" t="n">
         <v>46018</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -10089,7 +10229,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="R9" s="5" t="n">
         <v>46018</v>
       </c>
       <c r="S9" t="inlineStr">
@@ -10161,7 +10301,7 @@
           <t>WF_LS_251227_00001</t>
         </is>
       </c>
-      <c r="AM9" s="6" t="n">
+      <c r="AM9" s="5" t="n">
         <v>46018</v>
       </c>
       <c r="AN9" t="inlineStr">
@@ -10262,7 +10402,7 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -10290,7 +10430,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="R10" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="S10" t="inlineStr">
@@ -10372,7 +10512,7 @@
           <t>WF_LS_260101_00001</t>
         </is>
       </c>
-      <c r="AM10" s="6" t="n">
+      <c r="AM10" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="AN10" t="inlineStr">
@@ -10473,7 +10613,7 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -10501,7 +10641,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="S11" t="inlineStr">
@@ -10583,7 +10723,7 @@
           <t>WF_LS_260101_00002</t>
         </is>
       </c>
-      <c r="AM11" s="6" t="n">
+      <c r="AM11" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="AN11" t="inlineStr">
@@ -10684,7 +10824,7 @@
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="5" t="n">
         <v>46024</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -10712,7 +10852,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="5" t="n">
         <v>46024</v>
       </c>
       <c r="S12" t="inlineStr">
@@ -10794,7 +10934,7 @@
           <t>WF_LS_260102_00001</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="n">
+      <c r="AM12" s="5" t="n">
         <v>46024</v>
       </c>
       <c r="AN12" t="inlineStr">
@@ -10895,7 +11035,7 @@
       <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="5" t="n">
         <v>46047</v>
       </c>
       <c r="I13" t="inlineStr">
@@ -10923,7 +11063,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="5" t="n">
         <v>46047</v>
       </c>
       <c r="S13" t="inlineStr">
@@ -11005,7 +11145,7 @@
           <t>WF_LS_260125_00001</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="n">
+      <c r="AM13" s="5" t="n">
         <v>46047</v>
       </c>
       <c r="AN13" t="inlineStr">
@@ -11106,7 +11246,7 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="5" t="n">
         <v>46053</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -11134,7 +11274,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="5" t="n">
         <v>46053</v>
       </c>
       <c r="S14" t="inlineStr">
@@ -11206,7 +11346,7 @@
           <t>WF_LS_260131_00001</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="n">
+      <c r="AM14" s="5" t="n">
         <v>46053</v>
       </c>
       <c r="AN14" t="inlineStr">
@@ -11307,7 +11447,7 @@
       <c r="G15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="5" t="n">
         <v>46057</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -11335,7 +11475,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="5" t="n">
         <v>46057</v>
       </c>
       <c r="S15" t="inlineStr">
@@ -11417,7 +11557,7 @@
           <t>WF_LS_260204_00001</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="n">
+      <c r="AM15" s="5" t="n">
         <v>46057</v>
       </c>
       <c r="AN15" t="inlineStr">
@@ -11518,7 +11658,7 @@
       <c r="G16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="5" t="n">
         <v>46060</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -11546,7 +11686,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="5" t="n">
         <v>46060</v>
       </c>
       <c r="S16" t="inlineStr">
@@ -11628,7 +11768,7 @@
           <t>WF_LS_260207_00001</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="n">
+      <c r="AM16" s="5" t="n">
         <v>46060</v>
       </c>
       <c r="AN16" t="inlineStr">
@@ -11729,7 +11869,7 @@
       <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="5" t="n">
         <v>46063</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -11757,7 +11897,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="5" t="n">
         <v>46063</v>
       </c>
       <c r="S17" t="inlineStr">
@@ -11839,7 +11979,7 @@
           <t>WF_LS_260210_00001</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="n">
+      <c r="AM17" s="5" t="n">
         <v>46063</v>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11940,7 +12080,7 @@
       <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="5" t="n">
         <v>46065</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -11968,7 +12108,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="5" t="n">
         <v>46065</v>
       </c>
       <c r="S18" t="inlineStr">
@@ -12040,7 +12180,7 @@
           <t>WF_LS_260212_00001</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="n">
+      <c r="AM18" s="5" t="n">
         <v>46065</v>
       </c>
       <c r="AN18" t="inlineStr">
@@ -12141,7 +12281,7 @@
       <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="5" t="n">
         <v>46071</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -12169,7 +12309,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="5" t="n">
         <v>46071</v>
       </c>
       <c r="S19" t="inlineStr">
@@ -12251,7 +12391,7 @@
           <t>WF_LS_260218_00001</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="n">
+      <c r="AM19" s="5" t="n">
         <v>46071</v>
       </c>
       <c r="AN19" t="inlineStr">
@@ -12352,7 +12492,7 @@
       <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="5" t="n">
         <v>46076</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -12380,7 +12520,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="5" t="n">
         <v>46076</v>
       </c>
       <c r="S20" t="inlineStr">
@@ -12462,7 +12602,7 @@
           <t>WF_LS_260223_00001</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="n">
+      <c r="AM20" s="5" t="n">
         <v>46076</v>
       </c>
       <c r="AN20" t="inlineStr">
@@ -12563,7 +12703,7 @@
       <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="5" t="n">
         <v>46087</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -12591,7 +12731,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="5" t="n">
         <v>46087</v>
       </c>
       <c r="S21" t="inlineStr">
@@ -12673,7 +12813,7 @@
           <t>WF_LS_260306_00001</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="n">
+      <c r="AM21" s="5" t="n">
         <v>46087</v>
       </c>
       <c r="AN21" t="inlineStr">
@@ -12774,7 +12914,7 @@
       <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="5" t="n">
         <v>46093</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -12802,7 +12942,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="5" t="n">
         <v>46093</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -12884,7 +13024,7 @@
           <t>WF_LS_260312_00001</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="n">
+      <c r="AM22" s="5" t="n">
         <v>46093</v>
       </c>
       <c r="AN22" t="inlineStr">
@@ -12961,197 +13101,197 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>零售</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>营业</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n">
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n">
         <v>146</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="n">
+      <c r="F23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="7" t="n">
         <v>46096</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>15:53:27</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="4" t="n">
+      <c r="J23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="4" t="n">
+      <c r="L23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>已支付</t>
         </is>
       </c>
-      <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="5" t="n">
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="7" t="n">
         <v>46096</v>
       </c>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>15:53:50</t>
         </is>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="U23" s="4" t="inlineStr">
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>1636404775</t>
         </is>
       </c>
-      <c r="W23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" s="4" t="n">
+      <c r="W23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="Y23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="4" t="n"/>
-      <c r="AB23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="Y23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="6" t="n"/>
+      <c r="AB23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="6" t="inlineStr">
         <is>
           <t>零售</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AF23" s="6" t="inlineStr">
         <is>
           <t>万龙服务中心</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AG23" s="6" t="inlineStr">
         <is>
           <t>杨</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
+      <c r="AH23" s="6" t="inlineStr">
         <is>
           <t>18810482322</t>
         </is>
       </c>
-      <c r="AI23" s="4" t="inlineStr">
+      <c r="AI23" s="6" t="inlineStr">
         <is>
           <t>oHdTn5SJpEiRoOoUIudwrmFCOL2c</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="inlineStr">
+      <c r="AJ23" s="6" t="inlineStr">
         <is>
           <t>微信支付</t>
         </is>
       </c>
-      <c r="AK23" s="4" t="inlineStr">
+      <c r="AK23" s="6" t="inlineStr">
         <is>
           <t>1636404775</t>
         </is>
       </c>
-      <c r="AL23" s="4" t="inlineStr">
+      <c r="AL23" s="6" t="inlineStr">
         <is>
           <t>WF_LS_260315_00001</t>
         </is>
       </c>
-      <c r="AM23" s="5" t="n">
+      <c r="AM23" s="7" t="n">
         <v>46096</v>
       </c>
-      <c r="AN23" s="4" t="inlineStr">
+      <c r="AN23" s="6" t="inlineStr">
         <is>
           <t>15:53:27</t>
         </is>
       </c>
-      <c r="AO23" s="4" t="n"/>
-      <c r="AP23" s="4" t="n"/>
-      <c r="AQ23" s="4" t="n">
+      <c r="AO23" s="6" t="n"/>
+      <c r="AP23" s="6" t="n"/>
+      <c r="AQ23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="AR23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" s="4" t="n">
+      <c r="AR23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="AT23" s="4" t="inlineStr">
+      <c r="AT23" s="6" t="inlineStr">
         <is>
           <t>王政-工作号</t>
         </is>
       </c>
-      <c r="AU23" s="4" t="inlineStr">
+      <c r="AU23" s="6" t="inlineStr">
         <is>
           <t>oHdTn5XJcwBdMRtxKTG1vw5YBUH4</t>
         </is>
       </c>
-      <c r="AV23" s="4" t="n"/>
-      <c r="AW23" s="4" t="n"/>
-      <c r="AX23" s="4" t="inlineStr">
+      <c r="AV23" s="6" t="n"/>
+      <c r="AW23" s="6" t="n"/>
+      <c r="AX23" s="6" t="inlineStr">
         <is>
           <t>杨</t>
         </is>
       </c>
-      <c r="AY23" s="4" t="inlineStr">
+      <c r="AY23" s="6" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="AZ23" s="4" t="n"/>
-      <c r="BA23" s="4" t="n"/>
-      <c r="BB23" s="4" t="n"/>
-      <c r="BC23" s="4" t="n"/>
-      <c r="BD23" s="4" t="n"/>
-      <c r="BE23" s="4" t="n"/>
-      <c r="BF23" s="4" t="n"/>
-      <c r="BG23" s="4" t="n"/>
-      <c r="BH23" s="4" t="n"/>
-      <c r="BI23" s="4" t="n"/>
-      <c r="BJ23" s="4" t="n"/>
-      <c r="BK23" s="4" t="n"/>
+      <c r="AZ23" s="6" t="n"/>
+      <c r="BA23" s="6" t="n"/>
+      <c r="BB23" s="6" t="n"/>
+      <c r="BC23" s="6" t="n"/>
+      <c r="BD23" s="6" t="n"/>
+      <c r="BE23" s="6" t="n"/>
+      <c r="BF23" s="6" t="n"/>
+      <c r="BG23" s="6" t="n"/>
+      <c r="BH23" s="6" t="n"/>
+      <c r="BI23" s="6" t="n"/>
+      <c r="BJ23" s="6" t="n"/>
+      <c r="BK23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13178,7 +13318,7 @@
       <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="5" t="n">
         <v>46109</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -13206,7 +13346,7 @@
           <t>已支付</t>
         </is>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="5" t="n">
         <v>46109</v>
       </c>
       <c r="S24" t="inlineStr">
@@ -13288,7 +13428,7 @@
           <t>WF_LS_260328_00001</t>
         </is>
       </c>
-      <c r="AM24" s="6" t="n">
+      <c r="AM24" s="5" t="n">
         <v>46109</v>
       </c>
       <c r="AN24" t="inlineStr">
